--- a/output/pdf_financials_xlsx/CGII.xlsx
+++ b/output/pdf_financials_xlsx/CGII.xlsx
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.296728</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.101335</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.087022</v>
       </c>
     </row>
     <row r="35">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.296728</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.101335</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.087022</v>
       </c>
     </row>
     <row r="37">
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.499471</v>
+        <v>0.202743</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.126451</v>
+        <v>0.025116</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.158563</v>
+        <v>0.07154099999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">

--- a/output/pdf_financials_xlsx/CGII.xlsx
+++ b/output/pdf_financials_xlsx/CGII.xlsx
@@ -2205,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.023732</v>
       </c>
     </row>
     <row r="112">
@@ -2579,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.023732</v>
       </c>
     </row>
     <row r="135">
@@ -2595,7 +2595,7 @@
         <v>-0.357388</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.166746</v>
+        <v>-0.190478</v>
       </c>
     </row>
   </sheetData>
@@ -3887,7 +3887,11 @@
           <t>Purchase of equipment 7</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -3984,7 +3988,11 @@
           <t>Private placement 12</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>0.391338</v>
       </c>
